--- a/table/resources/sample/betsample/BetArea.xlsx
+++ b/table/resources/sample/betsample/BetArea.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="794"/>
+    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="BetArea" sheetId="21" r:id="rId1"/>
@@ -1962,7 +1962,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" hidden="1" spans="1:10">
+    <row r="3" s="1" customFormat="1" spans="1:10">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -1990,7 +1990,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" hidden="1" spans="2:10">
+    <row r="4" s="1" customFormat="1" spans="2:10">
       <c r="B4" s="2"/>
       <c r="C4" s="3"/>
       <c r="D4" s="2"/>
